--- a/import_template_product_variant/tests/sample_three_attributes_exists.xlsx
+++ b/import_template_product_variant/tests/sample_three_attributes_exists.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="49">
   <si>
     <t xml:space="preserve">product_tmpl_code</t>
   </si>
@@ -85,6 +85,9 @@
     <t xml:space="preserve">*TMPL*product_brand_id</t>
   </si>
   <si>
+    <t xml:space="preserve">route_ids</t>
+  </si>
+  <si>
     <t xml:space="preserve">PRODTMPL1TEST</t>
   </si>
   <si>
@@ -134,6 +137,9 @@
   </si>
   <si>
     <t xml:space="preserve">Brand 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Make To Order</t>
   </si>
   <si>
     <t xml:space="preserve">PROD1_WM</t>
@@ -172,7 +178,7 @@
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot; €&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -194,6 +200,14 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -238,7 +252,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -259,25 +273,29 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="false"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3" customBuiltin="false"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6" customBuiltin="false"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4" customBuiltin="false"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7" customBuiltin="false"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:U1048576"/>
-  <sheetFormatPr defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:V10"/>
+  <sheetFormatPr defaultColWidth="8.921875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18.89"/>
@@ -285,13 +303,13 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="20.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15.28"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="17.4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14.35"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="13.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="67.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="16" style="0" width="23.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="19" style="0" width="8.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="12.91"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -358,196 +376,208 @@
       <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="0" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>4050119164021</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K2" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L2" s="0" t="n">
         <v>10.5</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O2" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P2" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q2" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R2" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S2" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T2" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U2" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="V2" s="0" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>4050119164038</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K3" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L3" s="0" t="n">
         <v>20</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O3" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q3" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R3" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S3" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T3" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U3" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="V3" s="0" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>4050119164106</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K4" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L4" s="0" t="n">
         <v>25</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O4" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q4" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R4" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S4" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T4" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U4" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="V4" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" s="0" t="n">
         <v>10</v>
@@ -556,54 +586,54 @@
         <v>4050119164083</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L5" s="0" t="n">
         <v>10.5</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q5" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R5" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S5" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T5" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U5" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E6" s="0" t="n">
         <v>10</v>
@@ -612,106 +642,105 @@
         <v>4050119164090</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K6" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L6" s="0" t="n">
         <v>20</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q6" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R6" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S6" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T6" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U6" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E7" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K7" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L7" s="0" t="n">
         <v>25</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q7" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R7" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S7" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T7" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U7" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T10" s="5"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="P2" r:id="rId1" display="https://trey.es/web/content/58179?unique=f644e77ee21c04bc1b3c28e6b3094b95780a17cf"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/import_template_product_variant/tests/sample_three_attributes_exists.xlsx
+++ b/import_template_product_variant/tests/sample_three_attributes_exists.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="49">
   <si>
     <t xml:space="preserve">product_tmpl_code</t>
   </si>
@@ -64,10 +64,10 @@
     <t xml:space="preserve">*TMPL*invoice_policy</t>
   </si>
   <si>
-    <t xml:space="preserve">*TMPL*image</t>
-  </si>
-  <si>
-    <t xml:space="preserve">image_variant</t>
+    <t xml:space="preserve">*TMPL*image_1920</t>
+  </si>
+  <si>
+    <t xml:space="preserve">image_variant_1920</t>
   </si>
   <si>
     <t xml:space="preserve">*TMPL*description_sale</t>
@@ -85,6 +85,9 @@
     <t xml:space="preserve">*TMPL*product_brand_id</t>
   </si>
   <si>
+    <t xml:space="preserve">route_ids</t>
+  </si>
+  <si>
     <t xml:space="preserve">PRODTMPL1TEST</t>
   </si>
   <si>
@@ -130,10 +133,13 @@
     <t xml:space="preserve">Description for suppliers.</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit(s)</t>
+    <t xml:space="preserve">Units</t>
   </si>
   <si>
     <t xml:space="preserve">Brand 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replenish on Order (MTO)</t>
   </si>
   <si>
     <t xml:space="preserve">PROD1_WM</t>
@@ -172,7 +178,7 @@
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot; €&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -195,6 +201,14 @@
       <name val="Arial"/>
       <family val="0"/>
     </font>
+    <font>
+      <u val="single"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -238,7 +252,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -259,25 +273,37 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="false"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3" customBuiltin="false"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6" customBuiltin="false"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4" customBuiltin="false"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7" customBuiltin="false"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:U1048576"/>
-  <sheetFormatPr defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:V10"/>
+  <sheetFormatPr defaultColWidth="8.9453125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18.89"/>
@@ -285,13 +311,13 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="20.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15.28"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="17.4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14.35"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="13.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="67.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="16" style="0" width="23.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="19" style="0" width="8.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="12.91"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -337,7 +363,7 @@
       <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="0" t="s">
@@ -358,196 +384,208 @@
       <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="0" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>4050119164021</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K2" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L2" s="0" t="n">
         <v>10.5</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O2" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P2" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q2" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R2" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S2" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T2" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U2" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>4050119164038</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K3" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L3" s="0" t="n">
         <v>20</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O3" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q3" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R3" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S3" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T3" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U3" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="V3" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>4050119164106</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K4" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L4" s="0" t="n">
         <v>25</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O4" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q4" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R4" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S4" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T4" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U4" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="V4" s="6" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" s="0" t="n">
         <v>10</v>
@@ -556,54 +594,54 @@
         <v>4050119164083</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L5" s="0" t="n">
         <v>10.5</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q5" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R5" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S5" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T5" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U5" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E6" s="0" t="n">
         <v>10</v>
@@ -612,99 +650,98 @@
         <v>4050119164090</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K6" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L6" s="0" t="n">
         <v>20</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q6" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R6" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S6" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T6" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U6" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E7" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K7" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L7" s="0" t="n">
         <v>25</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q7" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R7" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S7" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T7" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U7" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T10" s="7"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="P2" r:id="rId1" display="https://trey.es/web/content/58179?unique=f644e77ee21c04bc1b3c28e6b3094b95780a17cf"/>
